--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.39971407988128</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.5955241045183375</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.6565633475704646</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.6927501634120065</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.7430013372817357</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.7619194340920972</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.7722140409003233</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.776083947298385</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7920067114391443</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.8061851185252895</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.8195480615138393</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.8329372364360768</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8610542463376933</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8849676244573073</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.9000288884597085</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.4827003691786831</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.5862046375290538</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.624299986543833</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.6526573130237494</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.6877478676827089</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.7201859630279248</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.749231913835362</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7706115547321984</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.7857089877763376</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7988019348055528</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.8167265491641832</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8359239543016832</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8544695012690392</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8687001502571556</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8817455030446308</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.4166438474933667</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.5704990323240964</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.599776462666977</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.6413519182160576</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.6789097802939201</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.7092094871069803</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.7309587998608578</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.7398875349672999</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.7600119244336038</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.795714736887387</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.8204945268604792</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.852285530627682</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8640568582392555</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8765027281045371</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8891960305652882</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.5666493634186014</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.5969116136903375</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.632409140913991</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6562588775739899</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.7031211391020437</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.7188980324920549</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.736487324323416</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7640566387356632</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.7959926618837719</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.8075392712488768</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.8272798679084823</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8501753612802189</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8768092556314619</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8910800275524695</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.9055894130810124</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.5674098416242943</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.600299164310921</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.6272219851062639</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.6612560030100949</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.7065304416890679</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.7313960210904156</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.7439920602042915</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7676243041556016</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7855031459421883</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7969463379045721</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.8084314445330066</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8374720576673169</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8667471757759525</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8832719546064225</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8944945845778732</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.4156101281484286</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.585363681891959</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.6902658434179475</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.7198827764038521</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.7592211124718864</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.7642027000788724</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.7773905445755399</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.7936921996006161</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.8038128223381202</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.8189345202131267</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.8515613433635862</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8639597695062303</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8847021642013381</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8912074798482026</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.9005493379440941</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.4707115856640527</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.563537225548004</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.6481341529091618</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.6854193111545537</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.6948161333901339</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.7364056591982743</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.7556119964357466</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.7709703327139974</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7906837302118201</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.8136208606596205</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.8339820331014496</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.8451095741111813</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8629315013639357</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8774663173653243</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.883541937342942</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.4706678347400782</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.5634508326808456</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.6471165333055444</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.6827591128261287</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.691016833954039</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.7272361383816037</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.7450863523152005</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.7533390477798068</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.7613735235682616</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.7736642619866099</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.789310328768001</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.7962858034392171</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.8105243024873933</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.8180551952069963</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.8296903785936633</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.4706272153817603</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.5634313147091903</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.6470599691801846</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.6827528485466388</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6910142662389313</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.7270814468634736</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.7450695633401551</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.7529632858906479</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.7605024392555543</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7723506474762027</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7889174583630594</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7952869567781043</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.8073663675691716</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.8143529280746155</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.8266905344201376</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.470671749514866</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.5634460122525748</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.6471753280553915</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.6828413282203416</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.6910250107195095</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.7277406667381013</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.7450043596214325</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.7534553150877468</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.7615937762447573</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.7741294562406141</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7885332900641528</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7963181540428607</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.8114827305034389</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.8261094547615158</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.8347632092038842</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.5773900869133095</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.6108129907914585</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.6535996682969742</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.6898267080245433</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.7225946380248878</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.7454535067860055</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7652358223851197</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7858424469284904</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.8032581933476834</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.816826225553023</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.8334637933730182</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8539353116440446</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8643927496067612</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8740740459048186</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8873843360342097</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.5778380460779797</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.631728142899179</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.6779349180972231</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6987476936462083</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.7267706949268833</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7571416894835674</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7766584089819228</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7975831715628867</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.8176149996411066</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.8351631660967904</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.843732751808157</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8511636758330665</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8600735419339657</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8682568834704895</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8774822687994157</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.4156015246740646</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.5853095119813612</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6899517686617664</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.7192859687474721</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.7576945769053163</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.7621668000223513</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.7730170419821886</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.7836516156921138</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7904121590641509</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7960094814360581</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.8144465953217001</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.8260037114019086</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.8438174443460502</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.847829261278029</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.8540868249948375</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.4155768880324383</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.5853361898950661</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6900143972784614</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.7193675386528431</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.7576970342148545</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.7621143265892912</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7728177747931295</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7832875058293514</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.7895942882605506</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.7943857825329711</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.8100582440251627</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.8202592167422702</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.8367137002928042</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.8405660077373898</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.8470740027216117</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.4155436803639811</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.5853426094468897</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.6899815603948207</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.7193088030652135</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.7575743225513863</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.762002662409095</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.7727077888260823</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7833019890355353</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7894570624348138</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.7941797386552022</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.8092131325634584</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.8187131440822751</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.8347967499867281</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.83862241910136</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.8439864160080369</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.4154618760652952</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.5853549235804192</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.6899573295014281</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.7193133509911095</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.7575803849952176</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.7620279115311133</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.7726115529788561</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7834395107019327</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7894763409405802</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7940756718816091</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.8093575050620264</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.8191185675825556</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.8342111308152941</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.8387353058969182</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.8430888264390227</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.5792711220095463</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.6131333473649686</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.6565856058189348</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.6863538540705061</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7344535597145865</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7634980794137247</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.7744465920602071</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7970689386810185</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.8154921897007217</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.8345185645831467</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.852053870637387</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8764566067812489</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8900036625860336</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8990452623306825</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.9136509083381875</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.5803044755938845</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.617690038098631</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.649300912719438</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.6866508847933502</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.7284483879711809</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.7406269626436219</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7607424628153621</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7911695647708148</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.8063639773731073</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.8232135386762007</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8390972974500711</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8583723646716981</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8710337633115277</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8820457512342531</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8944619953641036</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.5793417040802509</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.6137539624158477</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6647780553918194</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.7049129049736773</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.728663997223558</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7423587304352766</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.764568338599846</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7836714424679603</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7947938449692433</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.8086441995137956</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.8254682413849418</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8458751185364826</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8609180452859877</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8750461598412442</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8894226595639622</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.4816405532318496</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.5834540989317101</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.6206233185241432</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.6527530350560291</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.6979812446536626</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.7389560510992017</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.7576286301743744</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7832570355310097</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.8019818641559854</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.8129418074662194</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8255951366107063</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8400657687249877</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.855465043188059</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8690974543603881</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8850996743678747</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4807142873526224</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.5827929707119803</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.61719663986706</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.6474170105468994</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.6991755287748814</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.7322619214008158</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.767499410100829</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.7958985382562782</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.8077563846535631</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.8233907405452034</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8307720326616995</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8473248252436791</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8616382027286107</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8742067651222829</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8889905214273575</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.5753491962581352</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5998900889817985</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.6400714887063315</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.6491213924388604</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.6729734896576813</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.7158888742730651</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7529099995458357</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7759865157707448</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7958998850711783</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8296917063722282</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8562354455132337</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8741328737738161</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8871535328585343</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9033674635199158</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9182354887732468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.1635721133527047</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.2188894996193064</v>
+        <v>0.5943855142802754</v>
       </c>
       <c r="D24">
-        <v>0.2426033010183467</v>
+        <v>0.6732887803784725</v>
       </c>
       <c r="E24">
-        <v>0.2638718848300656</v>
+        <v>0.7216750877627389</v>
       </c>
       <c r="F24">
-        <v>0.4173184317273445</v>
+        <v>0.7460194558274197</v>
       </c>
       <c r="G24">
-        <v>0.4828492644660733</v>
+        <v>0.7563087745458741</v>
       </c>
       <c r="H24">
-        <v>0.5321772006717049</v>
+        <v>0.7637967859757117</v>
       </c>
       <c r="I24">
-        <v>0.5738584164938292</v>
+        <v>0.7747271936701474</v>
       </c>
       <c r="J24">
-        <v>0.6380099315075169</v>
+        <v>0.8094343573715357</v>
       </c>
       <c r="K24">
-        <v>0.6672251870884267</v>
+        <v>0.8350984765452544</v>
       </c>
       <c r="L24">
-        <v>0.7032283898438744</v>
+        <v>0.8585095908557183</v>
       </c>
       <c r="M24">
-        <v>0.766355328571293</v>
+        <v>0.8825181173221105</v>
       </c>
       <c r="N24">
-        <v>0.8156675964667905</v>
+        <v>0.8990998452327614</v>
       </c>
       <c r="O24">
-        <v>0.8560931104246112</v>
+        <v>0.9182839136315472</v>
       </c>
       <c r="P24">
-        <v>0.8722527314704942</v>
+        <v>0.9305027242120582</v>
+      </c>
+      <c r="Q24">
+        <v>0.9413595223648539</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.1604409885807319</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.2134065152467834</v>
+        <v>0.5939800647031274</v>
       </c>
       <c r="D25">
-        <v>0.2430817429080431</v>
+        <v>0.6761590320263929</v>
       </c>
       <c r="E25">
-        <v>0.3226818405821523</v>
+        <v>0.7360413829728104</v>
       </c>
       <c r="F25">
-        <v>0.3973187857273032</v>
+        <v>0.7656703583618454</v>
       </c>
       <c r="G25">
-        <v>0.4307031180694562</v>
+        <v>0.7882462186174913</v>
       </c>
       <c r="H25">
-        <v>0.528547028993223</v>
+        <v>0.7946247410688979</v>
       </c>
       <c r="I25">
-        <v>0.576890913665703</v>
+        <v>0.7988940685447028</v>
       </c>
       <c r="J25">
-        <v>0.6202369837744445</v>
+        <v>0.8510638279577369</v>
       </c>
       <c r="K25">
-        <v>0.6674455903172963</v>
+        <v>0.8660509278725008</v>
       </c>
       <c r="L25">
-        <v>0.7235356117963287</v>
+        <v>0.8799267863460819</v>
       </c>
       <c r="M25">
-        <v>0.7693246054676213</v>
+        <v>0.8984905698967574</v>
       </c>
       <c r="N25">
-        <v>0.8076263333158816</v>
+        <v>0.9102891279894892</v>
       </c>
       <c r="O25">
-        <v>0.838341921232544</v>
+        <v>0.9284019517710923</v>
       </c>
       <c r="P25">
-        <v>0.8612297970415652</v>
+        <v>0.9362496337733053</v>
+      </c>
+      <c r="Q25">
+        <v>0.9449519066162029</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.1457897046855144</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1771680253835196</v>
+        <v>0.6096902814014148</v>
       </c>
       <c r="D26">
-        <v>0.1933676518823471</v>
+        <v>0.6606352423224097</v>
       </c>
       <c r="E26">
-        <v>0.2281622199404477</v>
+        <v>0.7289261604622492</v>
       </c>
       <c r="F26">
-        <v>0.2937693922349242</v>
+        <v>0.7513954244659221</v>
       </c>
       <c r="G26">
-        <v>0.3525061950642142</v>
+        <v>0.7600301191437022</v>
       </c>
       <c r="H26">
-        <v>0.4194891392513047</v>
+        <v>0.7729372412270856</v>
       </c>
       <c r="I26">
-        <v>0.4571083135932796</v>
+        <v>0.7855854294338678</v>
       </c>
       <c r="J26">
-        <v>0.4643654167936099</v>
+        <v>0.812492244015329</v>
       </c>
       <c r="K26">
-        <v>0.516751030098306</v>
+        <v>0.8509368377747932</v>
       </c>
       <c r="L26">
-        <v>0.5421159262272912</v>
+        <v>0.8868459826112298</v>
       </c>
       <c r="M26">
-        <v>0.5924498874805413</v>
+        <v>0.903309372236306</v>
       </c>
       <c r="N26">
-        <v>0.6273277438906986</v>
+        <v>0.9187093989309507</v>
       </c>
       <c r="O26">
-        <v>0.6720665736221043</v>
+        <v>0.9318209836639505</v>
       </c>
       <c r="P26">
-        <v>0.6891030955556154</v>
+        <v>0.9422472537365379</v>
+      </c>
+      <c r="Q26">
+        <v>0.9489563175148027</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.1355009629472986</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.1676428791019744</v>
+        <v>0.6096486829923489</v>
       </c>
       <c r="D27">
-        <v>0.2526176670043661</v>
+        <v>0.6603041165024703</v>
       </c>
       <c r="E27">
-        <v>0.2706160706422978</v>
+        <v>0.728163850741975</v>
       </c>
       <c r="F27">
-        <v>0.3604864574692578</v>
+        <v>0.7478081782418431</v>
       </c>
       <c r="G27">
-        <v>0.4227238206885148</v>
+        <v>0.7565947649786658</v>
       </c>
       <c r="H27">
-        <v>0.4629561441011895</v>
+        <v>0.7655139199040402</v>
       </c>
       <c r="I27">
-        <v>0.5147617047124807</v>
+        <v>0.7721332301078728</v>
       </c>
       <c r="J27">
-        <v>0.5896718574216143</v>
+        <v>0.7861202501674949</v>
       </c>
       <c r="K27">
-        <v>0.6023216288080093</v>
+        <v>0.8046932682369383</v>
       </c>
       <c r="L27">
-        <v>0.631560223744716</v>
+        <v>0.8258884582338526</v>
       </c>
       <c r="M27">
-        <v>0.6835957425388952</v>
+        <v>0.8323860678922657</v>
       </c>
       <c r="N27">
-        <v>0.7027712709519516</v>
+        <v>0.8445727399956342</v>
       </c>
       <c r="O27">
-        <v>0.7451372365848032</v>
+        <v>0.8563635573445401</v>
       </c>
       <c r="P27">
-        <v>0.7656743456947979</v>
+        <v>0.875852026390093</v>
+      </c>
+      <c r="Q27">
+        <v>0.8813297812740499</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.5943855142802754</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.6732887803784725</v>
+        <v>0.5938844873818361</v>
       </c>
       <c r="D28">
-        <v>0.7216750877627389</v>
+        <v>0.6758642407080706</v>
       </c>
       <c r="E28">
-        <v>0.7460194558274197</v>
+        <v>0.7351521806108401</v>
       </c>
       <c r="F28">
-        <v>0.7563087745458741</v>
+        <v>0.7648400754984669</v>
       </c>
       <c r="G28">
-        <v>0.7637967859757117</v>
+        <v>0.7851320666679049</v>
       </c>
       <c r="H28">
-        <v>0.7747271936701474</v>
+        <v>0.7895945502706299</v>
       </c>
       <c r="I28">
-        <v>0.8094343573715357</v>
+        <v>0.7915831155247742</v>
       </c>
       <c r="J28">
-        <v>0.8350984765452544</v>
+        <v>0.8234235467968289</v>
       </c>
       <c r="K28">
-        <v>0.8585095908557183</v>
+        <v>0.8291263659002034</v>
       </c>
       <c r="L28">
-        <v>0.8825181173221105</v>
+        <v>0.8348669400287565</v>
       </c>
       <c r="M28">
-        <v>0.8990998452327614</v>
+        <v>0.8471448806266817</v>
       </c>
       <c r="N28">
-        <v>0.9182839136315472</v>
+        <v>0.8529411506593323</v>
       </c>
       <c r="O28">
-        <v>0.9305027242120582</v>
+        <v>0.8592287895834231</v>
       </c>
       <c r="P28">
-        <v>0.9413595223648539</v>
+        <v>0.8665977477295458</v>
+      </c>
+      <c r="Q28">
+        <v>0.8823412979581706</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.5939800647031274</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6761590320263929</v>
+        <v>0.5937942705093538</v>
       </c>
       <c r="D29">
-        <v>0.7360413829728104</v>
+        <v>0.6758721622209649</v>
       </c>
       <c r="E29">
-        <v>0.7656703583618454</v>
+        <v>0.7350793263587311</v>
       </c>
       <c r="F29">
-        <v>0.7882462186174913</v>
+        <v>0.7648625236233831</v>
       </c>
       <c r="G29">
-        <v>0.7946247410688979</v>
+        <v>0.7850168038175328</v>
       </c>
       <c r="H29">
-        <v>0.7988940685447028</v>
+        <v>0.7894487267160237</v>
       </c>
       <c r="I29">
-        <v>0.8510638279577369</v>
+        <v>0.7913719918393569</v>
       </c>
       <c r="J29">
-        <v>0.8660509278725008</v>
+        <v>0.8235774116250888</v>
       </c>
       <c r="K29">
-        <v>0.8799267863460819</v>
+        <v>0.8289589357157553</v>
       </c>
       <c r="L29">
-        <v>0.8984905698967574</v>
+        <v>0.8339049858659306</v>
       </c>
       <c r="M29">
-        <v>0.9102891279894892</v>
+        <v>0.8451015218093452</v>
       </c>
       <c r="N29">
-        <v>0.9284019517710923</v>
+        <v>0.8500993455645685</v>
       </c>
       <c r="O29">
-        <v>0.9362496337733053</v>
+        <v>0.8552204724059029</v>
       </c>
       <c r="P29">
-        <v>0.9449519066162029</v>
+        <v>0.8603634227366435</v>
+      </c>
+      <c r="Q29">
+        <v>0.8733807288778136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.6096902814014148</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.6606352423224097</v>
+        <v>0.5937256908817216</v>
       </c>
       <c r="D30">
-        <v>0.7289261604622492</v>
+        <v>0.6758553674261769</v>
       </c>
       <c r="E30">
-        <v>0.7513954244659221</v>
+        <v>0.7349801542244883</v>
       </c>
       <c r="F30">
-        <v>0.7600301191437022</v>
+        <v>0.7647970811336174</v>
       </c>
       <c r="G30">
-        <v>0.7729372412270856</v>
+        <v>0.7847951911010935</v>
       </c>
       <c r="H30">
-        <v>0.7855854294338678</v>
+        <v>0.7891709270423704</v>
       </c>
       <c r="I30">
-        <v>0.812492244015329</v>
+        <v>0.7910087650962464</v>
       </c>
       <c r="J30">
-        <v>0.8509368377747932</v>
+        <v>0.823155013556648</v>
       </c>
       <c r="K30">
-        <v>0.8868459826112298</v>
+        <v>0.8283391847708542</v>
       </c>
       <c r="L30">
-        <v>0.903309372236306</v>
+        <v>0.8332928044939516</v>
       </c>
       <c r="M30">
-        <v>0.9187093989309507</v>
+        <v>0.8441029008780836</v>
       </c>
       <c r="N30">
-        <v>0.9318209836639505</v>
+        <v>0.8488474648397227</v>
       </c>
       <c r="O30">
-        <v>0.9422472537365379</v>
+        <v>0.8535886173766485</v>
       </c>
       <c r="P30">
-        <v>0.9489563175148027</v>
+        <v>0.8582652834660558</v>
+      </c>
+      <c r="Q30">
+        <v>0.8699332453559279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.6096486829923489</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6603041165024703</v>
+        <v>0.5935572425247961</v>
       </c>
       <c r="D31">
-        <v>0.728163850741975</v>
+        <v>0.6758336966490137</v>
       </c>
       <c r="E31">
-        <v>0.7478081782418431</v>
+        <v>0.734802654496641</v>
       </c>
       <c r="F31">
-        <v>0.7565947649786658</v>
+        <v>0.7647745852847032</v>
       </c>
       <c r="G31">
-        <v>0.7655139199040402</v>
+        <v>0.7845226546275108</v>
       </c>
       <c r="H31">
-        <v>0.7721332301078728</v>
+        <v>0.7888089550774925</v>
       </c>
       <c r="I31">
-        <v>0.7861202501674949</v>
+        <v>0.7905336862921084</v>
       </c>
       <c r="J31">
-        <v>0.8046932682369383</v>
+        <v>0.8228360248472509</v>
       </c>
       <c r="K31">
-        <v>0.8258884582338526</v>
+        <v>0.8281406472839705</v>
       </c>
       <c r="L31">
-        <v>0.8323860678922657</v>
+        <v>0.8330881620979063</v>
       </c>
       <c r="M31">
-        <v>0.8445727399956342</v>
+        <v>0.8437002084102924</v>
       </c>
       <c r="N31">
-        <v>0.8563635573445401</v>
+        <v>0.8481647834951015</v>
       </c>
       <c r="O31">
-        <v>0.875852026390093</v>
+        <v>0.853148503686587</v>
       </c>
       <c r="P31">
-        <v>0.8813297812740499</v>
+        <v>0.8573069259313471</v>
+      </c>
+      <c r="Q31">
+        <v>0.8699689654080105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.5938844873818361</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6758642407080706</v>
+        <v>0.5939622880568161</v>
       </c>
       <c r="D32">
-        <v>0.7351521806108401</v>
+        <v>0.6759310079712582</v>
       </c>
       <c r="E32">
-        <v>0.7648400754984669</v>
+        <v>0.7354123886525776</v>
       </c>
       <c r="F32">
-        <v>0.7851320666679049</v>
+        <v>0.7650263158734852</v>
       </c>
       <c r="G32">
-        <v>0.7895945502706299</v>
+        <v>0.7856332327220359</v>
       </c>
       <c r="H32">
-        <v>0.7915831155247742</v>
+        <v>0.790254420068577</v>
       </c>
       <c r="I32">
-        <v>0.8234235467968289</v>
+        <v>0.7924791989265529</v>
       </c>
       <c r="J32">
-        <v>0.8291263659002034</v>
+        <v>0.8245408167416973</v>
       </c>
       <c r="K32">
-        <v>0.8348669400287565</v>
+        <v>0.8312108897337146</v>
       </c>
       <c r="L32">
-        <v>0.8471448806266817</v>
+        <v>0.8374354687288312</v>
       </c>
       <c r="M32">
-        <v>0.8529411506593323</v>
+        <v>0.8512087355437845</v>
       </c>
       <c r="N32">
-        <v>0.8592287895834231</v>
+        <v>0.8585770600772179</v>
       </c>
       <c r="O32">
-        <v>0.8665977477295458</v>
+        <v>0.8676053555479429</v>
       </c>
       <c r="P32">
-        <v>0.8823412979581706</v>
+        <v>0.8765396832256148</v>
+      </c>
+      <c r="Q32">
+        <v>0.8891207803366367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.5937942705093538</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.6758721622209649</v>
+        <v>0.5939454440209091</v>
       </c>
       <c r="D33">
-        <v>0.7350793263587311</v>
+        <v>0.6759247766424517</v>
       </c>
       <c r="E33">
-        <v>0.7648625236233831</v>
+        <v>0.7353814937456278</v>
       </c>
       <c r="F33">
-        <v>0.7850168038175328</v>
+        <v>0.7650181885099199</v>
       </c>
       <c r="G33">
-        <v>0.7894487267160237</v>
+        <v>0.7855808422137079</v>
       </c>
       <c r="H33">
-        <v>0.7913719918393569</v>
+        <v>0.7901763508375995</v>
       </c>
       <c r="I33">
-        <v>0.8235774116250888</v>
+        <v>0.7923734590860325</v>
       </c>
       <c r="J33">
-        <v>0.8289589357157553</v>
+        <v>0.8244649683411018</v>
       </c>
       <c r="K33">
-        <v>0.8339049858659306</v>
+        <v>0.8309279063861312</v>
       </c>
       <c r="L33">
-        <v>0.8451015218093452</v>
+        <v>0.8368349744085845</v>
       </c>
       <c r="M33">
-        <v>0.8500993455645685</v>
+        <v>0.8503189098453671</v>
       </c>
       <c r="N33">
-        <v>0.8552204724059029</v>
+        <v>0.8572369548616086</v>
       </c>
       <c r="O33">
-        <v>0.8603634227366435</v>
+        <v>0.8651833440474768</v>
       </c>
       <c r="P33">
-        <v>0.8733807288778136</v>
+        <v>0.8735378847006163</v>
+      </c>
+      <c r="Q33">
+        <v>0.8868651564534538</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.5937256908817216</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6758553674261769</v>
+        <v>0.593923284473685</v>
       </c>
       <c r="D34">
-        <v>0.7349801542244883</v>
+        <v>0.6759375203951065</v>
       </c>
       <c r="E34">
-        <v>0.7647970811336174</v>
+        <v>0.7353610443405248</v>
       </c>
       <c r="F34">
-        <v>0.7847951911010935</v>
+        <v>0.7650145508957334</v>
       </c>
       <c r="G34">
-        <v>0.7891709270423704</v>
+        <v>0.7855130475280587</v>
       </c>
       <c r="H34">
-        <v>0.7910087650962464</v>
+        <v>0.7900759531960563</v>
       </c>
       <c r="I34">
-        <v>0.823155013556648</v>
+        <v>0.7922264013304275</v>
       </c>
       <c r="J34">
-        <v>0.8283391847708542</v>
+        <v>0.8238722985316489</v>
       </c>
       <c r="K34">
-        <v>0.8332928044939516</v>
+        <v>0.8300291212746931</v>
       </c>
       <c r="L34">
-        <v>0.8441029008780836</v>
+        <v>0.8356231565233116</v>
       </c>
       <c r="M34">
-        <v>0.8488474648397227</v>
+        <v>0.848883220362429</v>
       </c>
       <c r="N34">
-        <v>0.8535886173766485</v>
+        <v>0.8552791945751891</v>
       </c>
       <c r="O34">
-        <v>0.8582652834660558</v>
+        <v>0.8625456172959106</v>
       </c>
       <c r="P34">
-        <v>0.8699332453559279</v>
+        <v>0.870318367270436</v>
+      </c>
+      <c r="Q34">
+        <v>0.8852986656731759</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.5935572425247961</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.6758336966490137</v>
+        <v>0.5938953931617513</v>
       </c>
       <c r="D35">
-        <v>0.734802654496641</v>
+        <v>0.6759756168678617</v>
       </c>
       <c r="E35">
-        <v>0.7647745852847032</v>
+        <v>0.7353829744792486</v>
       </c>
       <c r="F35">
-        <v>0.7845226546275108</v>
+        <v>0.7650423565144649</v>
       </c>
       <c r="G35">
-        <v>0.7888089550774925</v>
+        <v>0.7854771688102509</v>
       </c>
       <c r="H35">
-        <v>0.7905336862921084</v>
+        <v>0.7900134922971186</v>
       </c>
       <c r="I35">
-        <v>0.8228360248472509</v>
+        <v>0.7921352786149822</v>
       </c>
       <c r="J35">
-        <v>0.8281406472839705</v>
+        <v>0.8238356014705461</v>
       </c>
       <c r="K35">
-        <v>0.8330881620979063</v>
+        <v>0.8297400303495636</v>
       </c>
       <c r="L35">
-        <v>0.8437002084102924</v>
+        <v>0.8351346411075284</v>
       </c>
       <c r="M35">
-        <v>0.8481647834951015</v>
+        <v>0.8481584704842315</v>
       </c>
       <c r="N35">
-        <v>0.853148503686587</v>
+        <v>0.8541749123937001</v>
       </c>
       <c r="O35">
-        <v>0.8573069259313471</v>
+        <v>0.8608709076740054</v>
       </c>
       <c r="P35">
-        <v>0.8699689654080105</v>
+        <v>0.868034489546303</v>
+      </c>
+      <c r="Q35">
+        <v>0.8829178317749489</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.5939622880568161</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6759310079712582</v>
+        <v>0.5935833749015447</v>
       </c>
       <c r="D36">
-        <v>0.7354123886525776</v>
+        <v>0.676035916428154</v>
       </c>
       <c r="E36">
-        <v>0.7650263158734852</v>
+        <v>0.7350367032640674</v>
       </c>
       <c r="F36">
-        <v>0.7856332327220359</v>
+        <v>0.7649165917543481</v>
       </c>
       <c r="G36">
-        <v>0.790254420068577</v>
+        <v>0.784723357956649</v>
       </c>
       <c r="H36">
-        <v>0.7924791989265529</v>
+        <v>0.7889966189275125</v>
       </c>
       <c r="I36">
-        <v>0.8245408167416973</v>
+        <v>0.7908002812815949</v>
       </c>
       <c r="J36">
-        <v>0.8312108897337146</v>
+        <v>0.822460499777566</v>
       </c>
       <c r="K36">
-        <v>0.8374354687288312</v>
+        <v>0.8278653738976027</v>
       </c>
       <c r="L36">
-        <v>0.8512087355437845</v>
+        <v>0.8325157930419486</v>
       </c>
       <c r="M36">
-        <v>0.8585770600772179</v>
+        <v>0.8434724316244216</v>
       </c>
       <c r="N36">
-        <v>0.8676053555479429</v>
+        <v>0.8482102181091253</v>
       </c>
       <c r="O36">
-        <v>0.8765396832256148</v>
+        <v>0.8531304152650054</v>
       </c>
       <c r="P36">
-        <v>0.8891207803366367</v>
+        <v>0.8566815954335937</v>
+      </c>
+      <c r="Q36">
+        <v>0.8697860346759416</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.5939454440209091</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6759247766424517</v>
+        <v>0.6142582487798639</v>
       </c>
       <c r="D37">
-        <v>0.7353814937456278</v>
+        <v>0.7556894916071129</v>
       </c>
       <c r="E37">
-        <v>0.7650181885099199</v>
+        <v>0.761565717838412</v>
       </c>
       <c r="F37">
-        <v>0.7855808422137079</v>
+        <v>0.7740920881856276</v>
       </c>
       <c r="G37">
-        <v>0.7901763508375995</v>
+        <v>0.78544877371221</v>
       </c>
       <c r="H37">
-        <v>0.7923734590860325</v>
+        <v>0.8179554064032536</v>
       </c>
       <c r="I37">
-        <v>0.8244649683411018</v>
+        <v>0.8446306512211517</v>
       </c>
       <c r="J37">
-        <v>0.8309279063861312</v>
+        <v>0.8619202076224317</v>
       </c>
       <c r="K37">
-        <v>0.8368349744085845</v>
+        <v>0.8754379867958266</v>
       </c>
       <c r="L37">
-        <v>0.8503189098453671</v>
+        <v>0.8869971085291599</v>
       </c>
       <c r="M37">
-        <v>0.8572369548616086</v>
+        <v>0.9034183385379549</v>
       </c>
       <c r="N37">
-        <v>0.8651833440474768</v>
+        <v>0.9147383417086213</v>
       </c>
       <c r="O37">
-        <v>0.8735378847006163</v>
+        <v>0.9229278101458452</v>
       </c>
       <c r="P37">
-        <v>0.8868651564534538</v>
+        <v>0.9284313743891119</v>
+      </c>
+      <c r="Q37">
+        <v>0.9336851533979071</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.593923284473685</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6759375203951065</v>
+        <v>0.6151920748199853</v>
       </c>
       <c r="D38">
-        <v>0.7353610443405248</v>
+        <v>0.7529964899585742</v>
       </c>
       <c r="E38">
-        <v>0.7650145508957334</v>
+        <v>0.7580181389660003</v>
       </c>
       <c r="F38">
-        <v>0.7855130475280587</v>
+        <v>0.7671999606941418</v>
       </c>
       <c r="G38">
-        <v>0.7900759531960563</v>
+        <v>0.7859246301955639</v>
       </c>
       <c r="H38">
-        <v>0.7922264013304275</v>
+        <v>0.7975460355350013</v>
       </c>
       <c r="I38">
-        <v>0.8238722985316489</v>
+        <v>0.827704321966781</v>
       </c>
       <c r="J38">
-        <v>0.8300291212746931</v>
+        <v>0.8397485233384575</v>
       </c>
       <c r="K38">
-        <v>0.8356231565233116</v>
+        <v>0.8544550741429265</v>
       </c>
       <c r="L38">
-        <v>0.848883220362429</v>
+        <v>0.8718514017614276</v>
       </c>
       <c r="M38">
-        <v>0.8552791945751891</v>
+        <v>0.8786379958714337</v>
       </c>
       <c r="N38">
-        <v>0.8625456172959106</v>
+        <v>0.8889017780202771</v>
       </c>
       <c r="O38">
-        <v>0.870318367270436</v>
+        <v>0.8995580277892413</v>
       </c>
       <c r="P38">
-        <v>0.8852986656731759</v>
+        <v>0.9088090933964951</v>
+      </c>
+      <c r="Q38">
+        <v>0.9170066213160804</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.5938953931617513</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.6759756168678617</v>
+        <v>0.6159185309984683</v>
       </c>
       <c r="D39">
-        <v>0.7353829744792486</v>
+        <v>0.7522319131238415</v>
       </c>
       <c r="E39">
-        <v>0.7650423565144649</v>
+        <v>0.7566453214535851</v>
       </c>
       <c r="F39">
-        <v>0.7854771688102509</v>
+        <v>0.7645434086663434</v>
       </c>
       <c r="G39">
-        <v>0.7900134922971186</v>
+        <v>0.7808610208870242</v>
       </c>
       <c r="H39">
-        <v>0.7921352786149822</v>
+        <v>0.7903023730374604</v>
       </c>
       <c r="I39">
-        <v>0.8238356014705461</v>
+        <v>0.8095889225272604</v>
       </c>
       <c r="J39">
-        <v>0.8297400303495636</v>
+        <v>0.8227966129830177</v>
       </c>
       <c r="K39">
-        <v>0.8351346411075284</v>
+        <v>0.8354712153136734</v>
       </c>
       <c r="L39">
-        <v>0.8481584704842315</v>
+        <v>0.8486493372374394</v>
       </c>
       <c r="M39">
-        <v>0.8541749123937001</v>
+        <v>0.857813014846859</v>
       </c>
       <c r="N39">
-        <v>0.8608709076740054</v>
+        <v>0.8721102020170853</v>
       </c>
       <c r="O39">
-        <v>0.868034489546303</v>
+        <v>0.8823551102810178</v>
       </c>
       <c r="P39">
-        <v>0.8829178317749489</v>
+        <v>0.8907753599395258</v>
+      </c>
+      <c r="Q39">
+        <v>0.9048683069603649</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.5935833749015447</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.676035916428154</v>
+        <v>0.5808849171063557</v>
       </c>
       <c r="D40">
-        <v>0.7350367032640674</v>
+        <v>0.6147533012173123</v>
       </c>
       <c r="E40">
-        <v>0.7649165917543481</v>
+        <v>0.6963296168637121</v>
       </c>
       <c r="F40">
-        <v>0.784723357956649</v>
+        <v>0.7591113364667221</v>
       </c>
       <c r="G40">
-        <v>0.7889966189275125</v>
+        <v>0.7833524244426174</v>
       </c>
       <c r="H40">
-        <v>0.7908002812815949</v>
+        <v>0.7928571318862307</v>
       </c>
       <c r="I40">
-        <v>0.822460499777566</v>
+        <v>0.8122440729375369</v>
       </c>
       <c r="J40">
-        <v>0.8278653738976027</v>
+        <v>0.8265405805814069</v>
       </c>
       <c r="K40">
-        <v>0.8325157930419486</v>
+        <v>0.842750612209651</v>
       </c>
       <c r="L40">
-        <v>0.8434724316244216</v>
+        <v>0.8591791218888667</v>
       </c>
       <c r="M40">
-        <v>0.8482102181091253</v>
+        <v>0.874455707731477</v>
       </c>
       <c r="N40">
-        <v>0.8531304152650054</v>
+        <v>0.8849639105364147</v>
       </c>
       <c r="O40">
-        <v>0.8566815954335937</v>
+        <v>0.8951822761390409</v>
       </c>
       <c r="P40">
-        <v>0.8697860346759416</v>
+        <v>0.9030008138287837</v>
+      </c>
+      <c r="Q40">
+        <v>0.914018102372772</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.6142582487798639</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.7556894916071129</v>
+        <v>0.5771550871920064</v>
       </c>
       <c r="D41">
-        <v>0.761565717838412</v>
+        <v>0.637190095305301</v>
       </c>
       <c r="E41">
-        <v>0.7740920881856276</v>
+        <v>0.6842293651620457</v>
       </c>
       <c r="F41">
-        <v>0.78544877371221</v>
+        <v>0.7184945803818563</v>
       </c>
       <c r="G41">
-        <v>0.8179554064032536</v>
+        <v>0.7680299958516705</v>
       </c>
       <c r="H41">
-        <v>0.8446306512211517</v>
+        <v>0.8082776172633235</v>
       </c>
       <c r="I41">
-        <v>0.8619202076224317</v>
+        <v>0.8202753877479582</v>
       </c>
       <c r="J41">
-        <v>0.8754379867958266</v>
+        <v>0.8375022732066463</v>
       </c>
       <c r="K41">
-        <v>0.8869971085291599</v>
+        <v>0.8565956854737754</v>
       </c>
       <c r="L41">
-        <v>0.9034183385379549</v>
+        <v>0.8760516295636581</v>
       </c>
       <c r="M41">
-        <v>0.9147383417086213</v>
+        <v>0.8931755379263537</v>
       </c>
       <c r="N41">
-        <v>0.9229278101458452</v>
+        <v>0.9102694200655279</v>
       </c>
       <c r="O41">
-        <v>0.9284313743891119</v>
+        <v>0.9297760462562296</v>
       </c>
       <c r="P41">
-        <v>0.9336851533979071</v>
+        <v>0.9441518095471709</v>
+      </c>
+      <c r="Q41">
+        <v>0.9515129478633803</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.6151920748199853</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.7529964899585742</v>
+        <v>0.4848584755768054</v>
       </c>
       <c r="D42">
-        <v>0.7580181389660003</v>
+        <v>0.6030026157724064</v>
       </c>
       <c r="E42">
-        <v>0.7671999606941418</v>
+        <v>0.6530020305156469</v>
       </c>
       <c r="F42">
-        <v>0.7859246301955639</v>
+        <v>0.6981304782543043</v>
       </c>
       <c r="G42">
-        <v>0.7975460355350013</v>
+        <v>0.7366984580747424</v>
       </c>
       <c r="H42">
-        <v>0.827704321966781</v>
+        <v>0.7479094347838926</v>
       </c>
       <c r="I42">
-        <v>0.8397485233384575</v>
+        <v>0.7827875950729726</v>
       </c>
       <c r="J42">
-        <v>0.8544550741429265</v>
+        <v>0.8020995037738704</v>
       </c>
       <c r="K42">
-        <v>0.8718514017614276</v>
+        <v>0.8220930431805098</v>
       </c>
       <c r="L42">
-        <v>0.8786379958714337</v>
+        <v>0.8553438770692707</v>
       </c>
       <c r="M42">
-        <v>0.8889017780202771</v>
+        <v>0.876594507393214</v>
       </c>
       <c r="N42">
-        <v>0.8995580277892413</v>
+        <v>0.9116392490136072</v>
       </c>
       <c r="O42">
-        <v>0.9088090933964951</v>
+        <v>0.9193551079932077</v>
       </c>
       <c r="P42">
-        <v>0.9170066213160804</v>
+        <v>0.9286219593224345</v>
+      </c>
+      <c r="Q42">
+        <v>0.9364999707248161</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.6159185309984683</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.7522319131238415</v>
+        <v>0.5928748298584824</v>
       </c>
       <c r="D43">
-        <v>0.7566453214535851</v>
+        <v>0.6398465854552656</v>
       </c>
       <c r="E43">
-        <v>0.7645434086663434</v>
+        <v>0.6698093392969636</v>
       </c>
       <c r="F43">
-        <v>0.7808610208870242</v>
+        <v>0.7045079625656614</v>
       </c>
       <c r="G43">
-        <v>0.7903023730374604</v>
+        <v>0.7741779000640753</v>
       </c>
       <c r="H43">
-        <v>0.8095889225272604</v>
+        <v>0.797904621903159</v>
       </c>
       <c r="I43">
-        <v>0.8227966129830177</v>
+        <v>0.8120692492863961</v>
       </c>
       <c r="J43">
-        <v>0.8354712153136734</v>
+        <v>0.841111152620779</v>
       </c>
       <c r="K43">
-        <v>0.8486493372374394</v>
+        <v>0.8726145532561018</v>
       </c>
       <c r="L43">
-        <v>0.857813014846859</v>
+        <v>0.894252063490987</v>
       </c>
       <c r="M43">
-        <v>0.8721102020170853</v>
+        <v>0.9130858010073133</v>
       </c>
       <c r="N43">
-        <v>0.8823551102810178</v>
+        <v>0.9244409215866707</v>
       </c>
       <c r="O43">
-        <v>0.8907753599395258</v>
+        <v>0.9404194006020262</v>
       </c>
       <c r="P43">
-        <v>0.9048683069603649</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.5808849171063557</v>
-      </c>
-      <c r="C44">
-        <v>0.6147533012173123</v>
-      </c>
-      <c r="D44">
-        <v>0.6963296168637121</v>
-      </c>
-      <c r="E44">
-        <v>0.7591113364667221</v>
-      </c>
-      <c r="F44">
-        <v>0.7833524244426174</v>
-      </c>
-      <c r="G44">
-        <v>0.7928571318862307</v>
-      </c>
-      <c r="H44">
-        <v>0.8122440729375369</v>
-      </c>
-      <c r="I44">
-        <v>0.8265405805814069</v>
-      </c>
-      <c r="J44">
-        <v>0.842750612209651</v>
-      </c>
-      <c r="K44">
-        <v>0.8591791218888667</v>
-      </c>
-      <c r="L44">
-        <v>0.874455707731477</v>
-      </c>
-      <c r="M44">
-        <v>0.8849639105364147</v>
-      </c>
-      <c r="N44">
-        <v>0.8951822761390409</v>
-      </c>
-      <c r="O44">
-        <v>0.9030008138287837</v>
-      </c>
-      <c r="P44">
-        <v>0.914018102372772</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.5771550871920064</v>
-      </c>
-      <c r="C45">
-        <v>0.637190095305301</v>
-      </c>
-      <c r="D45">
-        <v>0.6842293651620457</v>
-      </c>
-      <c r="E45">
-        <v>0.7184945803818563</v>
-      </c>
-      <c r="F45">
-        <v>0.7680299958516705</v>
-      </c>
-      <c r="G45">
-        <v>0.8082776172633235</v>
-      </c>
-      <c r="H45">
-        <v>0.8202753877479582</v>
-      </c>
-      <c r="I45">
-        <v>0.8375022732066463</v>
-      </c>
-      <c r="J45">
-        <v>0.8565956854737754</v>
-      </c>
-      <c r="K45">
-        <v>0.8760516295636581</v>
-      </c>
-      <c r="L45">
-        <v>0.8931755379263537</v>
-      </c>
-      <c r="M45">
-        <v>0.9102694200655279</v>
-      </c>
-      <c r="N45">
-        <v>0.9297760462562296</v>
-      </c>
-      <c r="O45">
-        <v>0.9441518095471709</v>
-      </c>
-      <c r="P45">
-        <v>0.9515129478633803</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.4848584755768054</v>
-      </c>
-      <c r="C46">
-        <v>0.6030026157724064</v>
-      </c>
-      <c r="D46">
-        <v>0.6530020305156469</v>
-      </c>
-      <c r="E46">
-        <v>0.6981304782543043</v>
-      </c>
-      <c r="F46">
-        <v>0.7366984580747424</v>
-      </c>
-      <c r="G46">
-        <v>0.7479094347838926</v>
-      </c>
-      <c r="H46">
-        <v>0.7827875950729726</v>
-      </c>
-      <c r="I46">
-        <v>0.8020995037738704</v>
-      </c>
-      <c r="J46">
-        <v>0.8220930431805098</v>
-      </c>
-      <c r="K46">
-        <v>0.8553438770692707</v>
-      </c>
-      <c r="L46">
-        <v>0.876594507393214</v>
-      </c>
-      <c r="M46">
-        <v>0.9116392490136072</v>
-      </c>
-      <c r="N46">
-        <v>0.9193551079932077</v>
-      </c>
-      <c r="O46">
-        <v>0.9286219593224345</v>
-      </c>
-      <c r="P46">
-        <v>0.9364999707248161</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.5928748298584824</v>
-      </c>
-      <c r="C47">
-        <v>0.6398465854552656</v>
-      </c>
-      <c r="D47">
-        <v>0.6698093392969636</v>
-      </c>
-      <c r="E47">
-        <v>0.7045079625656614</v>
-      </c>
-      <c r="F47">
-        <v>0.7741779000640753</v>
-      </c>
-      <c r="G47">
-        <v>0.797904621903159</v>
-      </c>
-      <c r="H47">
-        <v>0.8120692492863961</v>
-      </c>
-      <c r="I47">
-        <v>0.841111152620779</v>
-      </c>
-      <c r="J47">
-        <v>0.8726145532561018</v>
-      </c>
-      <c r="K47">
-        <v>0.894252063490987</v>
-      </c>
-      <c r="L47">
-        <v>0.9130858010073133</v>
-      </c>
-      <c r="M47">
-        <v>0.9244409215866707</v>
-      </c>
-      <c r="N47">
-        <v>0.9404194006020262</v>
-      </c>
-      <c r="O47">
         <v>0.9457642217071143</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.9536827201750969</v>
       </c>
     </row>
